--- a/Unity/Assets/Config/Excel/NpcConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NpcConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25740" windowHeight="12945"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="NpcProto" sheetId="1" r:id="rId1"/>
@@ -615,7 +615,7 @@
     <t>ShopValue</t>
   </si>
   <si>
-    <t>NpcType</t>
+    <t>FuncitonID</t>
   </si>
   <si>
     <t>TaskID</t>
@@ -960,18 +960,18 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>

--- a/Unity/Assets/Config/Excel/NpcConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NpcConfig.xlsx
@@ -960,23 +960,23 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F6" s="15"/>
       <c r="G6" s="16">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="H6" s="16">
         <v>0</v>
@@ -2203,11 +2203,9 @@
       <c r="E7" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="16">
-        <v>10001201</v>
-      </c>
+      <c r="F7" s="16"/>
       <c r="G7" s="16">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="H7" s="16">
         <v>0</v>
@@ -2248,7 +2246,7 @@
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="16">
-        <v>1021</v>
+        <v>1001</v>
       </c>
       <c r="H8" s="16">
         <v>0</v>
@@ -2289,7 +2287,7 @@
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="16">
-        <v>1020</v>
+        <v>1001</v>
       </c>
       <c r="H9" s="16">
         <v>0</v>
@@ -2332,7 +2330,7 @@
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="16">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="H10" s="16">
         <v>0</v>
@@ -2373,7 +2371,7 @@
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="16">
-        <v>1015</v>
+        <v>1001</v>
       </c>
       <c r="H11" s="16">
         <v>0</v>
@@ -2412,11 +2410,9 @@
       <c r="E12" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="22">
-        <v>0</v>
-      </c>
+      <c r="F12" s="22"/>
       <c r="G12" s="16">
-        <v>1024</v>
+        <v>1001</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>64</v>
@@ -2454,7 +2450,7 @@
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="16">
-        <v>3</v>
+        <v>1001</v>
       </c>
       <c r="H13" s="16">
         <v>0</v>
@@ -2497,15 +2493,13 @@
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="16">
-        <v>2</v>
+        <v>1001</v>
       </c>
       <c r="H14" s="16">
         <v>0</v>
       </c>
       <c r="I14" s="16"/>
-      <c r="J14" s="17">
-        <v>2000002</v>
-      </c>
+      <c r="J14" s="17"/>
       <c r="K14" s="16"/>
       <c r="L14" s="18" t="s">
         <v>49</v>
@@ -2540,7 +2534,7 @@
       </c>
       <c r="F15" s="15"/>
       <c r="G15" s="16">
-        <v>1030</v>
+        <v>1001</v>
       </c>
       <c r="H15" s="16" t="s">
         <v>64</v>

--- a/Unity/Assets/Config/Excel/NpcConfig.xlsx
+++ b/Unity/Assets/Config/Excel/NpcConfig.xlsx
@@ -964,11 +964,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -977,6 +972,11 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
